--- a/slide_classification/TCGA_Results/Caption_based_aggregation/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -523,7 +523,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4</v>
+        <v>0.333333</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -692,10 +692,10 @@
         <v>0.42788</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>0.333333</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -867,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -953,7 +953,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1383,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>0.666667</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1641,7 +1641,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>0.666667</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2028,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2415,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2584,10 +2584,10 @@
         <v>0.6509160000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>0.666667</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2627,10 +2627,10 @@
         <v>0.694651</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>0.666667</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4</v>
+        <v>0.333333</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>1</v>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>0.333333</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>0.333333</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
@@ -3143,10 +3143,10 @@
         <v>0.97094</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.333333</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>1</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3404,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
         <v>1</v>
@@ -3576,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
         <v>1</v>
@@ -3662,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3705,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>1</v>
@@ -3791,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>0.333333</v>
       </c>
       <c r="J78" t="n">
         <v>1</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>1</v>
@@ -4261,10 +4261,10 @@
         <v>0.972614</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2</v>
+        <v>0.666667</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>1</v>
@@ -4562,10 +4562,10 @@
         <v>0.5752890000000001</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>0.666667</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -4608,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -4648,10 +4648,10 @@
         <v>0.464144</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4</v>
+        <v>0.666667</v>
       </c>
       <c r="J98" t="n">
         <v>1</v>
@@ -4694,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J99" t="n">
         <v>1</v>
@@ -4737,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
         <v>1</v>
@@ -4780,7 +4780,7 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>0.666667</v>
       </c>
       <c r="J101" t="n">
         <v>1</v>
@@ -4823,7 +4823,7 @@
         <v>1</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>0.666667</v>
       </c>
       <c r="J102" t="n">
         <v>1</v>
@@ -4866,7 +4866,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2</v>
+        <v>0.333333</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -14065,10 +14065,10 @@
         <v>0.127407</v>
       </c>
       <c r="H317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I317" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J317" t="n">
         <v>0</v>
@@ -14111,7 +14111,7 @@
         <v>0</v>
       </c>
       <c r="I318" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J318" t="n">
         <v>1</v>
@@ -14194,10 +14194,10 @@
         <v>0.593526</v>
       </c>
       <c r="H320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I320" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J320" t="n">
         <v>0</v>
@@ -14541,7 +14541,7 @@
         <v>0</v>
       </c>
       <c r="I328" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J328" t="n">
         <v>0</v>
@@ -14885,7 +14885,7 @@
         <v>0</v>
       </c>
       <c r="I336" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J336" t="n">
         <v>0</v>
@@ -15358,7 +15358,7 @@
         <v>0</v>
       </c>
       <c r="I347" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J347" t="n">
         <v>0</v>
@@ -15398,10 +15398,10 @@
         <v>0.437362</v>
       </c>
       <c r="H348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I348" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J348" t="n">
         <v>1</v>
@@ -15831,7 +15831,7 @@
         <v>0</v>
       </c>
       <c r="I358" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J358" t="n">
         <v>0</v>
@@ -16089,7 +16089,7 @@
         <v>1</v>
       </c>
       <c r="I364" t="n">
-        <v>0.666667</v>
+        <v>1</v>
       </c>
       <c r="J364" t="n">
         <v>1</v>
@@ -16562,7 +16562,7 @@
         <v>0</v>
       </c>
       <c r="I375" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J375" t="n">
         <v>0</v>
@@ -16648,7 +16648,7 @@
         <v>0</v>
       </c>
       <c r="I377" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J377" t="n">
         <v>0</v>
@@ -16731,10 +16731,10 @@
         <v>0.388509</v>
       </c>
       <c r="H379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I379" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J379" t="n">
         <v>1</v>
@@ -16774,10 +16774,10 @@
         <v>0.55035</v>
       </c>
       <c r="H380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I380" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J380" t="n">
         <v>1</v>
@@ -16860,10 +16860,10 @@
         <v>0.322636</v>
       </c>
       <c r="H382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I382" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J382" t="n">
         <v>1</v>
@@ -17419,10 +17419,10 @@
         <v>0.736923</v>
       </c>
       <c r="H395" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I395" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J395" t="n">
         <v>1</v>
@@ -18153,7 +18153,7 @@
         <v>0</v>
       </c>
       <c r="I412" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J412" t="n">
         <v>1</v>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.255971</v>
+        <v>0.191802</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.833725</v>
+        <v>0.937158</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.145829</v>
+        <v>0.075354</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.352621</v>
+        <v>0.457363</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -686,10 +686,10 @@
         <v>7.6e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.42788</v>
+        <v>0.598719</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.421667</v>
+        <v>0.459985</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.217185</v>
+        <v>0.210534</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.213784</v>
+        <v>0.160551</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -858,10 +858,10 @@
         <v>2.4e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.356159</v>
+        <v>0.523741</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.167995</v>
+        <v>0.104899</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5717410000000001</v>
+        <v>0.55484</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.235384</v>
+        <v>0.273838</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.358125</v>
+        <v>0.240834</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.220262</v>
+        <v>0.146024</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.381618</v>
+        <v>0.348559</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.169347</v>
+        <v>0.103443</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.247144</v>
+        <v>0.157063</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.151694</v>
+        <v>0.112439</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.150469</v>
+        <v>0.088091</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.140726</v>
+        <v>0.083132</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9457449999999999</v>
+        <v>0.757035</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.240444</v>
+        <v>0.133188</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.15357</v>
+        <v>0.100033</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.124131</v>
+        <v>0.084037</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.198817</v>
+        <v>0.204237</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.439369</v>
+        <v>0.306435</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.219282</v>
+        <v>0.169565</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.427537</v>
+        <v>0.215963</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.721374</v>
+        <v>0.541804</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.164883</v>
+        <v>0.087655</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.187861</v>
+        <v>0.140868</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.210316</v>
+        <v>0.169557</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.440589</v>
+        <v>0.345965</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.315331</v>
+        <v>0.200168</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.122463</v>
+        <v>0.127575</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.334393</v>
+        <v>0.163744</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.340567</v>
+        <v>0.29178</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.201466</v>
+        <v>0.118879</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.180427</v>
+        <v>0.243287</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.186066</v>
+        <v>0.153601</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.161052</v>
+        <v>0.095624</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.166608</v>
+        <v>0.143215</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.168352</v>
+        <v>0.141819</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.424061</v>
+        <v>0.413779</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.316133</v>
+        <v>0.335381</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.131224</v>
+        <v>0.08555</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.349667</v>
+        <v>0.233758</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.374526</v>
+        <v>0.351411</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2578,10 +2578,10 @@
         <v>0.08373700000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.6509160000000001</v>
+        <v>0.34565</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
@@ -2624,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>0.694651</v>
+        <v>0.748306</v>
       </c>
       <c r="H51" t="n">
         <v>1</v>
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.864376</v>
+        <v>0.951814</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.112365</v>
+        <v>0.115074</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.301173</v>
+        <v>0.275583</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0.00244</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.514581</v>
+        <v>0.460191</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.21539</v>
+        <v>0.111172</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.27405</v>
+        <v>0.224264</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.264028</v>
+        <v>0.221911</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0.516047</v>
+        <v>0.7067020000000001</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.588612</v>
+        <v>0.7298519999999999</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9720490000000001</v>
+        <v>0.989475</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -3094,10 +3094,10 @@
         <v>0.000826</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>0.456094</v>
+        <v>0.5878139999999999</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.97094</v>
+        <v>0.983618</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.353893</v>
+        <v>0.351684</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.469426</v>
+        <v>0.325762</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.192159</v>
+        <v>0.106101</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.264587</v>
+        <v>0.21335</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.214408</v>
+        <v>0.150485</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.177181</v>
+        <v>0.094129</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.234298</v>
+        <v>0.149578</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.442489</v>
+        <v>0.392873</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.164877</v>
+        <v>0.106124</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.192488</v>
+        <v>0.2051</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.306092</v>
+        <v>0.333546</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.22235</v>
+        <v>0.357168</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.550249</v>
+        <v>0.564297</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.879068</v>
+        <v>0.9650260000000001</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3785,7 +3785,7 @@
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.745764</v>
+        <v>0.689122</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.317878</v>
+        <v>0.394563</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.210747</v>
+        <v>0.125103</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.154865</v>
+        <v>0.104278</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.549608</v>
+        <v>0.661847</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3997,10 +3997,10 @@
         <v>0.00088</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.548252</v>
+        <v>0.385123</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.175513</v>
+        <v>0.090998</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.140954</v>
+        <v>0.089086</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.269819</v>
+        <v>0.175764</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.118199</v>
+        <v>0.07732</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.323954</v>
+        <v>0.238076</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.972614</v>
+        <v>0.985846</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.06103</v>
+        <v>0.033759</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.197906</v>
+        <v>0.138234</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.164409</v>
+        <v>0.139906</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.369916</v>
+        <v>0.215833</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.263448</v>
+        <v>0.196596</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.243473</v>
+        <v>0.21662</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0.5752890000000001</v>
+        <v>0.539674</v>
       </c>
       <c r="H96" t="n">
         <v>1</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.27961</v>
+        <v>0.188472</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4642,10 +4642,10 @@
         <v>0.000794</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>0.464144</v>
+        <v>0.620229</v>
       </c>
       <c r="H98" t="n">
         <v>1</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.984531</v>
+        <v>0.996371</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.420863</v>
+        <v>0.249691</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.976731</v>
+        <v>0.992659</v>
       </c>
       <c r="H101" t="n">
         <v>1</v>
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.999306</v>
+        <v>0.999856</v>
       </c>
       <c r="H102" t="n">
         <v>1</v>
@@ -4860,7 +4860,7 @@
         <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>0.557803</v>
+        <v>0.761958</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.22359</v>
+        <v>0.191806</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0.158753</v>
+        <v>0.187074</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -9160,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.819276</v>
+        <v>0.917468</v>
       </c>
       <c r="H203" t="n">
         <v>1</v>
@@ -9203,7 +9203,7 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>0.435042</v>
+        <v>0.448161</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0.198075</v>
+        <v>0.280177</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>0.670706</v>
+        <v>0.775925</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
         <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>0.449794</v>
+        <v>0.429562</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0.150438</v>
+        <v>0.255031</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.335774</v>
+        <v>0.30464</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>0.928231</v>
+        <v>0.937099</v>
       </c>
       <c r="H210" t="n">
         <v>1</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0.07281799999999999</v>
+        <v>0.133202</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>0.109618</v>
+        <v>0.157104</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>0.359901</v>
+        <v>0.316295</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0.111411</v>
+        <v>0.184245</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0.110117</v>
+        <v>0.148798</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
         <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>0.288099</v>
+        <v>0.3149</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0.180489</v>
+        <v>0.141736</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9805,7 +9805,7 @@
         <v>1</v>
       </c>
       <c r="G218" t="n">
-        <v>0.694724</v>
+        <v>0.705788</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9848,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0.425421</v>
+        <v>0.405768</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0.128783</v>
+        <v>0.164684</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>0.254349</v>
+        <v>0.291791</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -9974,10 +9974,10 @@
         <v>0.005515</v>
       </c>
       <c r="F222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G222" t="n">
-        <v>0.379924</v>
+        <v>0.500387</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0.135103</v>
+        <v>0.172826</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0.110748</v>
+        <v>0.162443</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>0.177757</v>
+        <v>0.238102</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>0.089227</v>
+        <v>0.17732</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="G227" t="n">
-        <v>0.6032380000000001</v>
+        <v>0.556964</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0.175692</v>
+        <v>0.225865</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0.097245</v>
+        <v>0.169509</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>0.169972</v>
+        <v>0.18742</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -10364,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.654827</v>
+        <v>0.563314</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0.26307</v>
+        <v>0.279098</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
         <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>0.9551500000000001</v>
+        <v>0.940627</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -10493,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>0.29925</v>
+        <v>0.340572</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="G235" t="n">
-        <v>0.876681</v>
+        <v>0.906964</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0.240677</v>
+        <v>0.242887</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0.09665799999999999</v>
+        <v>0.139432</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -10665,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0.117325</v>
+        <v>0.167174</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0.120236</v>
+        <v>0.162274</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0.143899</v>
+        <v>0.217109</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0.137332</v>
+        <v>0.192487</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0.079872</v>
+        <v>0.123575</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -10880,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>0.383565</v>
+        <v>0.324707</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -10923,7 +10923,7 @@
         <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>0.279231</v>
+        <v>0.303323</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -10963,10 +10963,10 @@
         <v>1e-06</v>
       </c>
       <c r="F245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G245" t="n">
-        <v>0.558762</v>
+        <v>0.480669</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -11009,7 +11009,7 @@
         <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>0.9134989999999999</v>
+        <v>0.897471</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -11052,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="G247" t="n">
-        <v>0.936401</v>
+        <v>0.9804890000000001</v>
       </c>
       <c r="H247" t="n">
         <v>1</v>
@@ -11095,7 +11095,7 @@
         <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>0.613559</v>
+        <v>0.761539</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0.998197</v>
+        <v>0.998812</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>0.381971</v>
+        <v>0.357772</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>0.153949</v>
+        <v>0.205369</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0.697917</v>
+        <v>0.844375</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>0.106296</v>
+        <v>0.121329</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>0.349635</v>
+        <v>0.26572</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -11393,10 +11393,10 @@
         <v>0.07790900000000001</v>
       </c>
       <c r="F255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>0.659305</v>
+        <v>0.460754</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>1</v>
       </c>
       <c r="G256" t="n">
-        <v>0.773929</v>
+        <v>0.811122</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -11482,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="G257" t="n">
-        <v>0.959619</v>
+        <v>0.978842</v>
       </c>
       <c r="H257" t="n">
         <v>1</v>
@@ -11525,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="G258" t="n">
-        <v>0.911843</v>
+        <v>0.892027</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>0.752217</v>
+        <v>0.91956</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>0.152949</v>
+        <v>0.177763</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0.567134</v>
+        <v>0.799596</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -11697,7 +11697,7 @@
         <v>0</v>
       </c>
       <c r="G262" t="n">
-        <v>0.463394</v>
+        <v>0.468586</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0.285395</v>
+        <v>0.270872</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11783,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>0.886352</v>
+        <v>0.9011400000000001</v>
       </c>
       <c r="H264" t="n">
         <v>1</v>
@@ -11826,7 +11826,7 @@
         <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>0.190241</v>
+        <v>0.233973</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>0.113599</v>
+        <v>0.166543</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.833805</v>
+        <v>0.829116</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="G268" t="n">
-        <v>0.750622</v>
+        <v>0.884702</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>0.210076</v>
+        <v>0.241171</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -12041,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0.209253</v>
+        <v>0.219351</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0.202286</v>
+        <v>0.179327</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
         <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>0.230316</v>
+        <v>0.264999</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -12167,10 +12167,10 @@
         <v>0.001145</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G273" t="n">
-        <v>0.392767</v>
+        <v>0.526786</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -12213,7 +12213,7 @@
         <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>0.301693</v>
+        <v>0.471517</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>0.204314</v>
+        <v>0.219646</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -12299,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="G276" t="n">
-        <v>0.503603</v>
+        <v>0.854612</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -12342,7 +12342,7 @@
         <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>0.3722</v>
+        <v>0.464181</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -12382,10 +12382,10 @@
         <v>0.001995</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G278" t="n">
-        <v>0.280664</v>
+        <v>0.56215</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>0.164041</v>
+        <v>0.1692</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>0.142209</v>
+        <v>0.183363</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -12514,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0.294973</v>
+        <v>0.272367</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>0.176226</v>
+        <v>0.149682</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>0.185051</v>
+        <v>0.204706</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>0.138484</v>
+        <v>0.131404</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -12686,7 +12686,7 @@
         <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>0.184431</v>
+        <v>0.219175</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>0.283756</v>
+        <v>0.274645</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -12772,7 +12772,7 @@
         <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>0.562568</v>
+        <v>0.666575</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12815,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>0.236093</v>
+        <v>0.28286</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>0.182267</v>
+        <v>0.2181</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="G290" t="n">
-        <v>0.12393</v>
+        <v>0.154306</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>0.209647</v>
+        <v>0.301515</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>0</v>
       </c>
       <c r="G292" t="n">
-        <v>0.209245</v>
+        <v>0.212298</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -13030,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>0.2973</v>
+        <v>0.431204</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0.151613</v>
+        <v>0.283267</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>0.171106</v>
+        <v>0.168528</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0.99949</v>
+        <v>0.999649</v>
       </c>
       <c r="H296" t="n">
         <v>1</v>
@@ -13202,7 +13202,7 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>0.571446</v>
+        <v>0.533663</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0.218834</v>
+        <v>0.256773</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         <v>0</v>
       </c>
       <c r="G299" t="n">
-        <v>0.412014</v>
+        <v>0.424217</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -13328,10 +13328,10 @@
         <v>0.894745</v>
       </c>
       <c r="F300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>0.40277</v>
+        <v>0.646308</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0.150479</v>
+        <v>0.176486</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="G302" t="n">
-        <v>0.215802</v>
+        <v>0.261328</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -13460,7 +13460,7 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0.972897</v>
+        <v>0.984127</v>
       </c>
       <c r="H303" t="n">
         <v>1</v>
@@ -13503,7 +13503,7 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0.993314</v>
+        <v>0.996889</v>
       </c>
       <c r="H304" t="n">
         <v>1</v>
@@ -13546,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>0.214036</v>
+        <v>0.282381</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>0.291835</v>
+        <v>0.405133</v>
       </c>
       <c r="H306" t="n">
         <v>1</v>
@@ -13632,7 +13632,7 @@
         <v>0</v>
       </c>
       <c r="G307" t="n">
-        <v>0.2743</v>
+        <v>0.30833</v>
       </c>
       <c r="H307" t="n">
         <v>1</v>
@@ -13675,7 +13675,7 @@
         <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>0.328324</v>
+        <v>0.343021</v>
       </c>
       <c r="H308" t="n">
         <v>1</v>
@@ -13718,7 +13718,7 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0.913899</v>
+        <v>0.978106</v>
       </c>
       <c r="H309" t="n">
         <v>1</v>
@@ -13761,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0.174179</v>
+        <v>0.183139</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
         <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>0.318616</v>
+        <v>0.35979</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.137905</v>
+        <v>0.169106</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0.28046</v>
+        <v>0.403326</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
